--- a/Bluetooth Box V3/BoxV3.xlsx
+++ b/Bluetooth Box V3/BoxV3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\123ba\Documents\Bluetooth Box V3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\123ba\Documents\KiCad\pcb-consortium\Bluetooth Box V3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC7AB9EE-8CAE-49A2-95A5-4F469D96BF07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8853C012-B4DC-4D3F-A18F-4A13C7203DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8550" yWindow="4470" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>Einkaufsliste</t>
   </si>
@@ -65,20 +65,57 @@
     <t>12V Akku</t>
   </si>
   <si>
-    <t>https://www.reichelt.de/de/de/shop/produkt/drehpotentiometer_stereo_10_kohm_logarithmisch_6_mm-73823</t>
-  </si>
-  <si>
-    <t>Potentiometer</t>
+    <t>PCB</t>
+  </si>
+  <si>
+    <t>LCSC components 1</t>
+  </si>
+  <si>
+    <t>LCSC components 2</t>
+  </si>
+  <si>
+    <t>Tang Band W3-1876S</t>
+  </si>
+  <si>
+    <t>https://www.soundimports.eu/de/tang-band-w3-1876s.html</t>
+  </si>
+  <si>
+    <t>GRS A25-2T</t>
+  </si>
+  <si>
+    <t>https://www.soundimports.eu/de/grs-a25-2t.html</t>
+  </si>
+  <si>
+    <t>Versand</t>
+  </si>
+  <si>
+    <t>Holz</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -101,14 +138,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Währung" xfId="1" builtinId="4"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -386,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F23"/>
+  <dimension ref="B2:F22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="28.7109375" customWidth="1"/>
@@ -401,9 +445,9 @@
       <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="E3">
-        <f>E6+E7+E8+E9+E10+E11+E12+E13+E14+E15+E16+E17+E18+E19+E20+E21+E22+E23</f>
-        <v>30.7</v>
+      <c r="E3" s="2">
+        <f>SUM(E6:E54)</f>
+        <v>203.97</v>
       </c>
       <c r="F3" t="s">
         <v>4</v>
@@ -416,10 +460,10 @@
       <c r="C5" t="s">
         <v>2</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F5" t="s">
@@ -433,10 +477,10 @@
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>27</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <f>C6*D6</f>
         <v>27</v>
       </c>
@@ -446,119 +490,153 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>2</v>
       </c>
-      <c r="D7">
-        <v>1.85</v>
-      </c>
-      <c r="E7">
-        <f t="shared" ref="E7:E23" si="0">C7*D7</f>
-        <v>3.7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
+      <c r="D7" s="1">
+        <v>4</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" ref="E7:E13" si="0">C7*D7</f>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E8">
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="E8" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>32.299999999999997</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E9">
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>15.34</v>
+      </c>
+      <c r="E9" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E10">
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1">
+        <v>69.95</v>
+      </c>
+      <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>69.95</v>
+      </c>
+      <c r="F10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E11">
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>39.950000000000003</v>
+      </c>
+      <c r="E11" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>39.950000000000003</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E12">
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>4.95</v>
+      </c>
+      <c r="E12" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E13">
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" s="1">
+        <v>6.48</v>
+      </c>
+      <c r="E13" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="2"/>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="2"/>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="E16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E19">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E21">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D17" s="1"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D18" s="1"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D19" s="1"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D20" s="1"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D21" s="1"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D22" s="1"/>
+      <c r="E22" s="2"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>